--- a/NuevaData/Presentacion/Investigacion/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Modelado y Simulación de Redes.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 5. ASPECTOS ACADÉMICOS Y RESULTADOS DE APRENDIZAJE/b. Resultados de Aprendizaje a nivel microcurricular/Syllabus AA-FR-003/Énfasis en Teleinformática/Modelado y Simulación de Redes.xlsx
@@ -2706,13 +2706,29 @@
       <c r="J35" s="47"/>
     </row>
     <row r="36" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
+      <c r="A36" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula modelos matemáticos de redes de comunicaciones.</t>
+        </is>
+      </c>
       <c r="B36" s="60"/>
-      <c r="C36" s="73"/>
+      <c r="C36" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Comprender</t>
+        </is>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="74"/>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA01</t>
+        </is>
+      </c>
+      <c r="G36" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explicar el proceso de modelado matemático en ingeniería de redes y las técnicas de evaluación analítica, experimental y por simulación.</t>
+        </is>
+      </c>
       <c r="H36" s="75"/>
       <c r="I36" s="76"/>
       <c r="J36" s="47"/>
@@ -2720,23 +2736,51 @@
     <row r="37" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="61"/>
       <c r="B37" s="62"/>
-      <c r="C37" s="41"/>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D37" s="41"/>
       <c r="E37" s="41"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="74"/>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA02</t>
+        </is>
+      </c>
+      <c r="G37" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modelar sistemas de comunicaciones mediante cadenas de Markov en tiempo discreto y continuo y procesos de nacimiento y muerte.</t>
+        </is>
+      </c>
       <c r="H37" s="75"/>
       <c r="I37" s="76"/>
       <c r="J37" s="47"/>
     </row>
     <row r="38" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59"/>
+      <c r="A38" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analiza el desempeño de redes mediante la teoría de colas.</t>
+        </is>
+      </c>
       <c r="B38" s="60"/>
-      <c r="C38" s="41"/>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="74"/>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA03</t>
+        </is>
+      </c>
+      <c r="G38" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calcular medidas de desempeño en colas determinísticas y markovianas y en redes de colas.</t>
+        </is>
+      </c>
       <c r="H38" s="75"/>
       <c r="I38" s="76"/>
       <c r="J38" s="47"/>
@@ -2744,11 +2788,23 @@
     <row r="39" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="50"/>
       <c r="B39" s="77"/>
-      <c r="C39" s="41"/>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D39" s="41"/>
       <c r="E39" s="41"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="66"/>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA04</t>
+        </is>
+      </c>
+      <c r="G39" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analizar colas con tiempos de servicio y procesos de llegada generales, y con prioridades, reservas, vacaciones o sondeo.</t>
+        </is>
+      </c>
       <c r="H39" s="67"/>
       <c r="I39" s="68"/>
       <c r="J39" s="47"/>
@@ -2756,23 +2812,51 @@
     <row r="40" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="61"/>
       <c r="B40" s="62"/>
-      <c r="C40" s="41"/>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="61"/>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA05</t>
+        </is>
+      </c>
+      <c r="G40" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analizar la integración de flujos elásticos y en tiempo real y modelar el tráfico de paquetes de voz (MMDP) y de video (MMPP) en canales compartidos.</t>
+        </is>
+      </c>
       <c r="H40" s="78"/>
       <c r="I40" s="62"/>
       <c r="J40" s="47"/>
     </row>
     <row r="41" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59"/>
+      <c r="A41" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evalúa modelos de redes mediante simulación y análisis estadístico.</t>
+        </is>
+      </c>
       <c r="B41" s="60"/>
-      <c r="C41" s="63"/>
+      <c r="C41" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Evaluar</t>
+        </is>
+      </c>
       <c r="D41" s="64"/>
       <c r="E41" s="65"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="66"/>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA06</t>
+        </is>
+      </c>
+      <c r="G41" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseñar experimentos de simulación de eventos discretos y contrastar sus resultados con los analíticos mediante intervalos de confianza.</t>
+        </is>
+      </c>
       <c r="H41" s="67"/>
       <c r="I41" s="68"/>
       <c r="J41" s="14"/>
@@ -2780,23 +2864,51 @@
     <row r="42" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="61"/>
       <c r="B42" s="62"/>
-      <c r="C42" s="63"/>
+      <c r="C42" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Analizar</t>
+        </is>
+      </c>
       <c r="D42" s="64"/>
       <c r="E42" s="65"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="66"/>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA07</t>
+        </is>
+      </c>
+      <c r="G42" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caracterizar el tráfico con dependencia de rango largo (autosimilitud y parámetro de Hurst) y estimar su efecto en el desempeño de los buffers.</t>
+        </is>
+      </c>
       <c r="H42" s="67"/>
       <c r="I42" s="68"/>
       <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="59"/>
+      <c r="A43" s="59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diseña mecanismos de calidad de servicio para redes.</t>
+        </is>
+      </c>
       <c r="B43" s="60"/>
-      <c r="C43" s="63"/>
+      <c r="C43" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Evaluar</t>
+        </is>
+      </c>
       <c r="D43" s="64"/>
       <c r="E43" s="65"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="66"/>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA08</t>
+        </is>
+      </c>
+      <c r="G43" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluar mecanismos de calidad de servicio (regulación de tráfico, disciplinas de servicio y gestión activa de colas) para ofrecer garantías a los usuarios.</t>
+        </is>
+      </c>
       <c r="H43" s="67"/>
       <c r="I43" s="68"/>
       <c r="J43" s="14"/>
@@ -3021,9 +3133,17 @@
       </c>
       <c r="B58" s="100"/>
       <c r="C58" s="100"/>
-      <c r="D58" s="101"/>
+      <c r="D58" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E58" s="101"/>
-      <c r="F58" s="101"/>
+      <c r="F58" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G58" s="101"/>
       <c r="H58" s="101"/>
       <c r="I58" s="101"/>
@@ -3035,9 +3155,17 @@
       </c>
       <c r="B59" s="100"/>
       <c r="C59" s="100"/>
-      <c r="D59" s="102"/>
+      <c r="D59" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E59" s="102"/>
-      <c r="F59" s="101"/>
+      <c r="F59" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G59" s="101"/>
       <c r="H59" s="102"/>
       <c r="I59" s="101"/>
@@ -3049,9 +3177,17 @@
       </c>
       <c r="B60" s="100"/>
       <c r="C60" s="100"/>
-      <c r="D60" s="101"/>
+      <c r="D60" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E60" s="101"/>
-      <c r="F60" s="101"/>
+      <c r="F60" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G60" s="101"/>
       <c r="H60" s="101"/>
       <c r="I60" s="102"/>
@@ -3063,9 +3199,17 @@
       </c>
       <c r="B61" s="100"/>
       <c r="C61" s="100"/>
-      <c r="D61" s="101"/>
+      <c r="D61" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E61" s="101"/>
-      <c r="F61" s="101"/>
+      <c r="F61" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G61" s="101"/>
       <c r="H61" s="101"/>
       <c r="I61" s="101"/>
@@ -3077,11 +3221,19 @@
       </c>
       <c r="B62" s="100"/>
       <c r="C62" s="100"/>
-      <c r="D62" s="102"/>
+      <c r="D62" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E62" s="102"/>
       <c r="F62" s="101"/>
       <c r="G62" s="101"/>
-      <c r="H62" s="102"/>
+      <c r="H62" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="I62" s="101"/>
       <c r="J62" s="98"/>
     </row>
@@ -3091,11 +3243,19 @@
       </c>
       <c r="B63" s="100"/>
       <c r="C63" s="100"/>
-      <c r="D63" s="102"/>
+      <c r="D63" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E63" s="102"/>
       <c r="F63" s="101"/>
       <c r="G63" s="101"/>
-      <c r="H63" s="102"/>
+      <c r="H63" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="I63" s="101"/>
       <c r="J63" s="98"/>
     </row>
@@ -3105,7 +3265,11 @@
       </c>
       <c r="B64" s="100"/>
       <c r="C64" s="100"/>
-      <c r="D64" s="102"/>
+      <c r="D64" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="E64" s="102"/>
       <c r="F64" s="101"/>
       <c r="G64" s="101"/>
@@ -3123,7 +3287,11 @@
       <c r="E65" s="102"/>
       <c r="F65" s="101"/>
       <c r="G65" s="101"/>
-      <c r="H65" s="102"/>
+      <c r="H65" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="I65" s="101"/>
       <c r="J65" s="98"/>
     </row>
@@ -3147,11 +3315,23 @@
       </c>
       <c r="B67" s="100"/>
       <c r="C67" s="100"/>
-      <c r="D67" s="102"/>
+      <c r="D67" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
       <c r="E67" s="102"/>
-      <c r="F67" s="102"/>
+      <c r="F67" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EE</t>
+        </is>
+      </c>
       <c r="G67" s="102"/>
-      <c r="H67" s="102"/>
+      <c r="H67" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
       <c r="I67" s="102"/>
       <c r="J67" s="98"/>
     </row>
@@ -3161,11 +3341,23 @@
       </c>
       <c r="B68" s="100"/>
       <c r="C68" s="100"/>
-      <c r="D68" s="102"/>
+      <c r="D68" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40%</t>
+        </is>
+      </c>
       <c r="E68" s="102"/>
-      <c r="F68" s="102"/>
+      <c r="F68" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
       <c r="G68" s="102"/>
-      <c r="H68" s="102"/>
+      <c r="H68" s="102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
       <c r="I68" s="102"/>
       <c r="J68" s="98"/>
     </row>
@@ -3175,11 +3367,23 @@
       </c>
       <c r="B69" s="100"/>
       <c r="C69" s="100"/>
-      <c r="D69" s="17"/>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
       <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
       <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
       <c r="I69" s="17"/>
       <c r="J69" s="98"/>
     </row>
